--- a/Logbook_KP.xlsx
+++ b/Logbook_KP.xlsx
@@ -1,185 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myRepo\sistem-informasi-manajemen-koperasi-tribuanaIV\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{422EEE17-40B1-43D7-A45C-4B50C97E999E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Logbook KP" sheetId="1" r:id="rId1"/>
+    <sheet name="Logbook KP 150 Jam" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Hari</t>
-  </si>
-  <si>
-    <t>Tanggal</t>
-  </si>
-  <si>
-    <t>Durasi (Jam)</t>
-  </si>
-  <si>
-    <t>Jenis Kegiatan</t>
-  </si>
-  <si>
-    <t>Deskripsi</t>
-  </si>
-  <si>
-    <t>Hasil Kegiatan</t>
-  </si>
-  <si>
-    <t>Senin</t>
-  </si>
-  <si>
-    <t>13 Juli 2026</t>
-  </si>
-  <si>
-    <t>Analisis Kebutuhan Sistem &amp; Wawancara</t>
-  </si>
-  <si>
-    <t>Melakukan observasi dan wawancara dengan pihak Koperasi mengenai alur bisnis.</t>
-  </si>
-  <si>
-    <t>Terkumpulnya spesifikasi kebutuhan sistem (SRS) dan pemahaman alur kerja koperasi.</t>
-  </si>
-  <si>
-    <t>20 Juli 2026</t>
-  </si>
-  <si>
-    <t>Perancangan Mockup &amp; Desain Antarmuka</t>
-  </si>
-  <si>
-    <t>Merancang tata letak visual (wireframe) dan alur interaksi pengguna (UI/UX).</t>
-  </si>
-  <si>
-    <t>Desain halaman dashboard, form input, dan tabel data yang telah disetujui.</t>
-  </si>
-  <si>
-    <t>Kamis</t>
-  </si>
-  <si>
-    <t>23 Juli 2026</t>
-  </si>
-  <si>
-    <t>Perancangan Basis Data (Database Design &amp; ERD)</t>
-  </si>
-  <si>
-    <t>Merancang arsitektur database relasional untuk menampung seluruh entitas data sistem.</t>
-  </si>
-  <si>
-    <t>Terbentuknya skema database MySQL (db_koperasi) dan relasi antar tabel.</t>
-  </si>
-  <si>
-    <t>3 Agustus 2026</t>
-  </si>
-  <si>
-    <t>Inisialisasi Backend &amp; Keamanan Sistem</t>
-  </si>
-  <si>
-    <t>Membangun server API menggunakan Node.js dan mengimplementasikan sistem login JWT.</t>
-  </si>
-  <si>
-    <t>Backend berjalan dengan sistem keamanan role-based untuk proteksi rute aplikasi.</t>
-  </si>
-  <si>
-    <t>Sabtu</t>
-  </si>
-  <si>
-    <t>8 Agustus 2026</t>
-  </si>
-  <si>
-    <t>Pembangunan Struktur Frontend</t>
-  </si>
-  <si>
-    <t>Melakukan setup framework Vue 3 dan Tailwind CSS, serta mengonfigurasi routing halaman.</t>
-  </si>
-  <si>
-    <t>Kerangka dasar web (Admin Layout) yang responsif siap digunakan.</t>
-  </si>
-  <si>
-    <t>15 Agustus 2026</t>
-  </si>
-  <si>
-    <t>Pengembangan Modul Master Data</t>
-  </si>
-  <si>
-    <t>Membangun fitur CRUD untuk entitas inti yaitu data Barang, Anggota, dan Supplier.</t>
-  </si>
-  <si>
-    <t>Administrator dapat menambah, mengedit, dan menghapus data utama secara terpusat.</t>
-  </si>
-  <si>
-    <t>22 Agustus 2026</t>
-  </si>
-  <si>
-    <t>Pengembangan Modul Pembelian (PO) &amp; Gudang</t>
-  </si>
-  <si>
-    <t>Membangun sistem pencatatan pasokan masuk dari supplier (Purchase Order) dan mutasi stok.</t>
-  </si>
-  <si>
-    <t>Sistem pengawasan pergerakan stok gudang secara otomatis dan riwayat PO.</t>
-  </si>
-  <si>
-    <t>27 Agustus 2026</t>
-  </si>
-  <si>
-    <t>Pengembangan Mesin Kasir (Point of Sales)</t>
-  </si>
-  <si>
-    <t>Mengembangkan fitur transaksi digital khusus untuk Kasir Swalayan dan Kasir Grosir.</t>
-  </si>
-  <si>
-    <t>Transaksi penjualan berjalan real-time dengan fitur pemotongan stok otomatis.</t>
-  </si>
-  <si>
-    <t>Selasa</t>
-  </si>
-  <si>
-    <t>1 September 2026</t>
-  </si>
-  <si>
-    <t>Migrasi &amp; Normalisasi Data Excel</t>
-  </si>
-  <si>
-    <t>Mengimpor dan memproses pembersihan ribuan data mentah dari file Excel lama ke database baru.</t>
-  </si>
-  <si>
-    <t>Data barang dan supplier terstruktur rapi tanpa duplikasi (bebas data redundan).</t>
-  </si>
-  <si>
-    <t>10 September 2026</t>
-  </si>
-  <si>
-    <t>Pembuatan Laporan Akuntansi &amp; Pengujian Sistem</t>
-  </si>
-  <si>
-    <t>Mengembangkan fitur rekapitulasi laporan jurnal akuntansi dan melakukan pengujian aplikasi (UAT).</t>
-  </si>
-  <si>
-    <t>Sistem mampu mencetak laporan keuangan komprehensif dan aplikasi dinyatakan siap pakai.</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -216,14 +72,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -548,276 +396,412 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G17"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
     <col min="5" max="5" width="45.83203125" customWidth="1"/>
-    <col min="6" max="6" width="90.83203125" customWidth="1"/>
+    <col min="6" max="6" width="95.83203125" customWidth="1"/>
     <col min="7" max="7" width="80.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>No</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Hari</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Tanggal</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Durasi (Jam)</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Jenis Kegiatan</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Deskripsi</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Hasil Kegiatan</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
+      <c r="B2" t="str">
+        <v>Senin</v>
+      </c>
+      <c r="C2" t="str">
+        <v>13 Juli 2026</v>
       </c>
       <c r="D2">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Orientasi &amp; Analisis Kebutuhan Sistem</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Pengenalan lingkungan Koperasi dan wawancara awal dengan pengurus terkait masalah pencatatan manual.</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Memahami ruang lingkup proyek dan menyusun spesifikasi kebutuhan sistem (SRS).</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
+      <c r="B3" t="str">
+        <v>Kamis</v>
+      </c>
+      <c r="C3" t="str">
+        <v>16 Juli 2026</v>
       </c>
       <c r="D3">
-        <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Pengumpulan &amp; Pemetaan Data Master</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Mengumpulkan sampel data mentah (Excel) meliputi data Barang, Supplier, dan Anggota Koperasi.</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Identifikasi atribut data yang wajib masuk ke dalam sistem informasi.</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
+      <c r="B4" t="str">
+        <v>Senin</v>
+      </c>
+      <c r="C4" t="str">
+        <v>20 Juli 2026</v>
       </c>
       <c r="D4">
-        <v>7</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Perancangan Alur Sistem (Flowchart)</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Merancang diagram alir data (Data Flow Diagram) untuk proses pembelian, stok, dan kasir.</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Dokumen alur logika aplikasi yang disetujui oleh pembimbing lapangan.</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
+      <c r="B5" t="str">
+        <v>Kamis</v>
+      </c>
+      <c r="C5" t="str">
+        <v>23 Juli 2026</v>
       </c>
       <c r="D5">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Perancangan Antarmuka Pengguna (UI/UX)</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Membuat purwarupa visual (wireframe &amp; mockup) dari dashboard Admin dan Kasir.</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Terbentuknya rancangan desain tampilan web yang responsif dan siap coding.</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
+      <c r="B6" t="str">
+        <v>Selasa</v>
+      </c>
+      <c r="C6" t="str">
+        <v>28 Juli 2026</v>
       </c>
       <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Perancangan Basis Data (ERD &amp; Skema)</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Menentukan entitas, relasi, tipe data, dan struktur tabel di database relasional.</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Dokumen ERD dan terbentuknya kerangka database MySQL (db_koperasi).</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
+      <c r="B7" t="str">
+        <v>Sabtu</v>
+      </c>
+      <c r="C7" t="str">
+        <v>1 Agustus 2026</v>
       </c>
       <c r="D7">
-        <v>8</v>
-      </c>
-      <c r="E7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Setup Lingkungan Pengembangan (Backend)</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Menginisiasi proyek server menggunakan Node.js, Express, dan konektivitas database.</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Backend server berhasil berjalan dan terhubung sempurna ke MySQL.</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
+      <c r="B8" t="str">
+        <v>Rabu</v>
+      </c>
+      <c r="C8" t="str">
+        <v>5 Agustus 2026</v>
       </c>
       <c r="D8">
-        <v>7</v>
-      </c>
-      <c r="E8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Implementasi Keamanan &amp; Autentikasi JWT</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Mengembangkan modul login, enkripsi password (Bcrypt), dan JWT (JSON Web Token).</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Sistem perlindungan rute berbasis hak akses (role-based) untuk Admin dan Kasir.</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
+      <c r="B9" t="str">
+        <v>Senin</v>
+      </c>
+      <c r="C9" t="str">
+        <v>10 Agustus 2026</v>
       </c>
       <c r="D9">
-        <v>8</v>
-      </c>
-      <c r="E9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Pembangunan Struktur Layout Frontend</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Melakukan inisialisasi Vue 3, Tailwind CSS, Vue Router, dan integrasi State Management (Pinia).</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Kerangka layout dashboard utama dengan navigasi sidebar yang interaktif.</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" t="s">
-        <v>43</v>
+      <c r="B10" t="str">
+        <v>Jumat</v>
+      </c>
+      <c r="C10" t="str">
+        <v>14 Agustus 2026</v>
       </c>
       <c r="D10">
-        <v>7</v>
-      </c>
-      <c r="E10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Modul CRUD Master Data</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Membangun antarmuka dan endpoint API untuk kelola data Barang, Anggota, dan Supplier.</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Administrator dapat melakukan aksi Tambah, Edit, Hapus, dan Pencarian Data terpusat.</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>47</v>
+      <c r="B11" t="str">
+        <v>Rabu</v>
+      </c>
+      <c r="C11" t="str">
+        <v>19 Agustus 2026</v>
       </c>
       <c r="D11">
-        <v>8</v>
-      </c>
-      <c r="E11" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" t="s">
-        <v>50</v>
+        <v>10</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Modul Pembelian (PO) &amp; Gudang</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Merancang fitur dokumen Purchase Order dan mutasi masuk barang dari supplier.</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Transaksi stok dari supplier dapat menambah stok gudang secara otomatis.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Senin</v>
+      </c>
+      <c r="C12" t="str">
+        <v>24 Agustus 2026</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Modul Transaksi Kasir (Point of Sales)</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Mengembangkan mesin kasir digital untuk divisi Swalayan (Satuan) dan Grosir (Grosir/Kartonan).</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Keranjang belanja berfungsi real-time menghitung total tagihan dan memotong stok toko.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Sabtu</v>
+      </c>
+      <c r="C13" t="str">
+        <v>29 Agustus 2026</v>
+      </c>
+      <c r="D13">
+        <v>10</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Migrasi &amp; Normalisasi Data Excel Mentah</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Mengembangkan skrip Node.js untuk mengekstrak, membersihkan duplikasi, dan mengimpor data Excel lama.</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Basis data aplikasi terisi ribuan data historis yang bersih dan tervalidasi.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Kamis</v>
+      </c>
+      <c r="C14" t="str">
+        <v>3 September 2026</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Modul Laporan Jurnal Akuntansi</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Membangun algoritma untuk merekapitulasi setiap pergerakan uang dan stok menjadi laporan keuangan.</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Sistem mencetak laporan pemasukan/pengeluaran yang terstruktur sesuai standar akuntansi.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Selasa</v>
+      </c>
+      <c r="C15" t="str">
+        <v>8 September 2026</v>
+      </c>
+      <c r="D15">
+        <v>10</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Pengujian Sistem (Testing &amp; UAT)</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Melakukan serangkaian pengujian integrasi (end-to-end) bersama calon pengguna dari Koperasi.</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Menemukan dan mendokumentasikan bug minor untuk persiapan perbaikan tahap akhir.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Sabtu</v>
+      </c>
+      <c r="C16" t="str">
+        <v>12 September 2026</v>
+      </c>
+      <c r="D16">
+        <v>10</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Bug-Fixing, Evaluasi, &amp; Penyusunan Laporan</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Melakukan perbaikan bug, finalisasi performa aplikasi, serta menyusun buku Laporan Kerja Praktik (KP).</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Aplikasi berstatus siap deploy (Production-Ready) dan buku laporan KP rampung.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v/>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v>Total Keseluruhan:</v>
+      </c>
+      <c r="D17">
+        <v>150</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G11" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G17"/>
   </ignoredErrors>
 </worksheet>
 </file>